--- a/calibration_plots/plot_data_wine_mpbart.xlsx
+++ b/calibration_plots/plot_data_wine_mpbart.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,15 +368,15 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.6601111111111111</v>
+        <v>0.6861111111111111</v>
       </c>
       <c r="B2">
-        <v>0.8666666666666667</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.8699569892473118</v>
+        <v>0.8938285714285714</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -384,7 +384,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.9328735632183908</v>
+        <v>0.9477777777777778</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -392,7 +392,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.9617471264367816</v>
+        <v>0.9741111111111111</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -400,17 +400,9 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.9792</v>
+        <v>0.9921523809523809</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>0.9932873563218391</v>
-      </c>
-      <c r="B7">
         <v>1</v>
       </c>
     </row>
